--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104596_W16.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104596_W16.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6454</v>
+        <v>2.2971</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1902</v>
+        <v>1.0547</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4552</v>
+        <v>1.2423</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2957</v>
+        <v>1.2794</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9093</v>
+        <v>0.8968</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3865</v>
+        <v>0.3827</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0037</v>
+        <v>1.9657</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2255</v>
+        <v>1.1991</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7782</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.708</v>
+        <v>-0.6863</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3513</v>
+        <v>1.008</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5474</v>
+        <v>0.4548</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8038999999999999</v>
+        <v>0.5532</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.3627</v>
+        <v>-1.3562</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.3627</v>
+        <v>-1.3562</v>
       </c>
     </row>
     <row r="3">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4391</v>
+        <v>1.0048</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5505</v>
+        <v>-1.158</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9896</v>
+        <v>2.1628</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9547</v>
+        <v>-0.9636</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.5625</v>
+        <v>-1.576</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6078</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.4457</v>
+        <v>-1.4666</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.483</v>
+        <v>-1.5038</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M3" t="n">
-        <v>0.491</v>
+        <v>0.503</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0795</v>
+        <v>-0.0722</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2597</v>
+        <v>0.8302</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8953</v>
+        <v>0.3085</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3644</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. TOBEY</t>
+          <t>M. SALVO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3591</v>
+        <v>0.7169</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1283</v>
+        <v>-1.0357</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7692</v>
+        <v>1.7526</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.3513</v>
+        <v>-0.9949</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0159</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.3354</v>
+        <v>-0.3916</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1874</v>
+        <v>-1.4559</v>
       </c>
       <c r="K4" t="n">
-        <v>0.599</v>
+        <v>-0.7035</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7864</v>
+        <v>-0.7524</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1639</v>
+        <v>0.4609</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6149</v>
+        <v>0.1002</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.549</v>
+        <v>0.3608</v>
       </c>
       <c r="P4" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4421</v>
+        <v>0.8013</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3157</v>
+        <v>0.4202</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1264</v>
+        <v>0.3812</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2867</v>
+        <v>0.4104</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4977</v>
+        <v>-0.4222</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7844</v>
+        <v>0.8325</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1678</v>
+        <v>-1.1724</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.616</v>
+        <v>-0.6229</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5517</v>
+        <v>-0.5496</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6247</v>
+        <v>-0.6425</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1243</v>
+        <v>0.1099</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5431</v>
+        <v>-0.53</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6813</v>
+        <v>1.8104</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2612</v>
+        <v>1.3585</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4201</v>
+        <v>0.452</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. SALVO</t>
+          <t>M. TOBEY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1282</v>
+        <v>-0.4148</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3581</v>
+        <v>0.2661</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4862</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0006</v>
+        <v>-1.346</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6061</v>
+        <v>-0.0144</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3945</v>
+        <v>-1.3315</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.4488</v>
+        <v>-0.2003</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6998</v>
+        <v>0.5893</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.749</v>
+        <v>-0.7896</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4483</v>
+        <v>-1.1457</v>
       </c>
       <c r="N6" t="n">
-        <v>0.09370000000000001</v>
+        <v>-0.6037</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3546</v>
+        <v>-0.5419</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2214</v>
+        <v>0.6549</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0907</v>
+        <v>0.4665</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1306</v>
+        <v>0.1884</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.12</v>
+        <v>-0.4978</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3428</v>
+        <v>-1.7513</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4628</v>
+        <v>1.2536</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5486</v>
+        <v>-1.5488</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.645</v>
+        <v>-0.6462</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9036</v>
+        <v>-0.9026999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5727</v>
+        <v>-1.5793</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0241</v>
+        <v>0.0305</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5344</v>
+        <v>-0.0871</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2299</v>
+        <v>-0.1721</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3046</v>
+        <v>0.0849</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9089</v>
+        <v>-1.4198</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.9164</v>
+        <v>-2.3511</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0075</v>
+        <v>0.9313</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2188</v>
+        <v>-0.2249</v>
       </c>
       <c r="H8" t="n">
         <v>0.5916</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8104</v>
+        <v>-0.8166</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.022</v>
+        <v>-0.0397</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3565</v>
+        <v>0.348</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3786</v>
+        <v>-0.3877</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1967</v>
+        <v>-0.1852</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3953</v>
+        <v>0.101</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6261</v>
+        <v>-0.0351</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2308</v>
+        <v>0.1361</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1174</v>
+        <v>-1.8881</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6506</v>
+        <v>-2.3199</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5332</v>
+        <v>0.4318</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.71</v>
+        <v>-3.7106</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7778</v>
+        <v>-0.7729</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.9321</v>
+        <v>-2.9378</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.1011</v>
+        <v>-2.1188</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1834</v>
+        <v>0.1756</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.2844</v>
+        <v>-2.2945</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6089</v>
+        <v>-1.5918</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P9" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1101</v>
+        <v>0.3412</v>
       </c>
       <c r="T9" t="n">
-        <v>0.127</v>
+        <v>0.485</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0169</v>
+        <v>-0.1438</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5591</v>
+        <v>-0.5674</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.4498</v>
+        <v>-0.4584</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. WONG</t>
+          <t>A. ALBICY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.726</v>
+        <v>-3.7626</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.6707</v>
+        <v>-4.503</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9447</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.5738</v>
+        <v>-3.2864</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.9189</v>
+        <v>-0.9713000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.6549</v>
+        <v>-2.315</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.1453</v>
+        <v>-1.6525</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.8235</v>
+        <v>0.1207</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.3218</v>
+        <v>-1.7731</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4285</v>
+        <v>-1.6339</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0954</v>
+        <v>-1.092</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3331</v>
+        <v>-0.5419</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1342</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.361</v>
+        <v>-2.5039</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2698</v>
+        <v>-0.3673</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2571</v>
+        <v>-0.3466</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0127</v>
+        <v>-0.0207</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9834000000000001</v>
+        <v>-0.1089</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ALBICY</t>
+          <t>I. WONG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4215</v>
+        <v>-3.8463</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.0735</v>
+        <v>-5.8761</v>
       </c>
       <c r="F11" t="n">
-        <v>0.652</v>
+        <v>2.0299</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.2924</v>
+        <v>-5.5908</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9814000000000001</v>
+        <v>-2.9317</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.311</v>
+        <v>-2.6592</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.6408</v>
+        <v>-5.1767</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1212</v>
+        <v>-2.8451</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.762</v>
+        <v>-2.3317</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6516</v>
+        <v>-0.4141</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1026</v>
+        <v>-0.0866</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.549</v>
+        <v>-0.3275</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.4952</v>
+        <v>-1.3658</v>
       </c>
       <c r="R11" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0198</v>
+        <v>-0.3741</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9376</v>
+        <v>-0.4231</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0823</v>
+        <v>0.049</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1093</v>
+        <v>0.9805</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. BRUSSINO</t>
+          <t>B. ANGOLA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.2419</v>
+        <v>-6.6098</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.275499999999999</v>
+        <v>-6.517</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0336</v>
+        <v>-0.0929</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.0397</v>
+        <v>-4.295</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.798</v>
+        <v>-2.8916</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.2417</v>
+        <v>-1.4034</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.1903</v>
+        <v>-3.0916</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6549</v>
+        <v>-1.9143</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.5354</v>
+        <v>-1.1773</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8494</v>
+        <v>-1.2034</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1431</v>
+        <v>-0.9774</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7063</v>
+        <v>-0.226</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5878</v>
+        <v>-3.8697</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.7635</v>
+        <v>-5.6908</v>
       </c>
       <c r="R12" t="n">
-        <v>3.1757</v>
+        <v>1.8211</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4124</v>
+        <v>1.0102</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3217</v>
+        <v>0.6312</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0907</v>
+        <v>0.379</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2019</v>
+        <v>0.5447</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2019</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B. ANGOLA</t>
+          <t>N. BRUSSINO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.4945</v>
+        <v>-6.891</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.3059</v>
+        <v>-7.9571</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1886</v>
+        <v>1.066</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.2809</v>
+        <v>-3.0376</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.8814</v>
+        <v>-0.7957</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.3994</v>
+        <v>-2.2419</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.0533</v>
+        <v>-2.2078</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.8884</v>
+        <v>-0.6657</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.1649</v>
+        <v>-1.542</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2275</v>
+        <v>-0.8298</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.993</v>
+        <v>-0.13</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2345</v>
+        <v>-0.6998</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.8562</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.6708</v>
+        <v>-4.7803</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8147</v>
+        <v>3.1868</v>
       </c>
       <c r="S13" t="n">
-        <v>0.09619999999999999</v>
+        <v>-1.0616</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2208</v>
+        <v>-0.969</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3169</v>
+        <v>-0.0926</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5463</v>
+        <v>-1.1984</v>
       </c>
       <c r="W13" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0927</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-21.9317</v>
+        <v>-20.901</v>
       </c>
       <c r="E14" t="n">
-        <v>-33.3232</v>
+        <v>-32.5706</v>
       </c>
       <c r="F14" t="n">
-        <v>11.3914</v>
+        <v>11.6694</v>
       </c>
       <c r="G14" t="n">
-        <v>-24.8429</v>
+        <v>-24.8916</v>
       </c>
       <c r="H14" t="n">
-        <v>-10.3021</v>
+        <v>-10.3376</v>
       </c>
       <c r="I14" t="n">
-        <v>-14.5404</v>
+        <v>-14.5542</v>
       </c>
       <c r="J14" t="n">
-        <v>-17.4284</v>
+        <v>-17.666</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.726100000000001</v>
+        <v>-5.8794</v>
       </c>
       <c r="L14" t="n">
-        <v>-11.7024</v>
+        <v>-11.7865</v>
       </c>
       <c r="M14" t="n">
-        <v>-7.4142</v>
+        <v>-7.2258</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.5761</v>
+        <v>-4.4581</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.838000000000001</v>
+        <v>-2.7675</v>
       </c>
       <c r="P14" t="n">
-        <v>2.268400000000001</v>
+        <v>2.2765</v>
       </c>
       <c r="Q14" t="n">
-        <v>-19.2808</v>
+        <v>-19.3487</v>
       </c>
       <c r="R14" t="n">
-        <v>21.5493</v>
+        <v>21.625</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5992</v>
+        <v>4.667099999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>1.103900000000001</v>
+        <v>2.1788</v>
       </c>
       <c r="U14" t="n">
-        <v>2.4951</v>
+        <v>2.4884</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.9567</v>
+        <v>-2.952999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2819</v>
+        <v>2.2653</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.2386</v>
+        <v>-5.2181</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. EJIM</t>
+          <t>M. JIMENEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.5764</v>
+        <v>5.2577</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0939</v>
+        <v>0.6011</v>
       </c>
       <c r="F15" t="n">
-        <v>5.6703</v>
+        <v>4.6566</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3911</v>
+        <v>5.0973</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1139</v>
+        <v>1.8038</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2772</v>
+        <v>3.2935</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5838</v>
+        <v>2.973</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4475</v>
+        <v>1.4167</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.8637</v>
+        <v>1.5563</v>
       </c>
       <c r="M15" t="n">
-        <v>2.8073</v>
+        <v>2.1244</v>
       </c>
       <c r="N15" t="n">
-        <v>1.6664</v>
+        <v>0.3871</v>
       </c>
       <c r="O15" t="n">
-        <v>1.1409</v>
+        <v>1.7372</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>1.707</v>
+        <v>0.388</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0484</v>
+        <v>-0.0955</v>
       </c>
       <c r="U15" t="n">
-        <v>1.7553</v>
+        <v>0.4835</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. JIMENEZ</t>
+          <t>M. EJIM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.2542</v>
+        <v>4.7073</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7476</v>
+        <v>-0.2452</v>
       </c>
       <c r="F16" t="n">
-        <v>4.5066</v>
+        <v>4.9525</v>
       </c>
       <c r="G16" t="n">
-        <v>5.1012</v>
+        <v>3.392</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8066</v>
+        <v>3.1134</v>
       </c>
       <c r="I16" t="n">
-        <v>3.2946</v>
+        <v>0.2786</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9948</v>
+        <v>0.5621</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4302</v>
+        <v>1.4339</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5646</v>
+        <v>-0.8718</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1064</v>
+        <v>2.8299</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3764</v>
+        <v>1.6795</v>
       </c>
       <c r="O16" t="n">
-        <v>1.73</v>
+        <v>1.1504</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3799</v>
+        <v>0.8389</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0212</v>
+        <v>-0.1652</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3587</v>
+        <v>1.0041</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.9317</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.9093</v>
+        <v>4.5169</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7824</v>
+        <v>-1.2152</v>
       </c>
       <c r="F17" t="n">
-        <v>5.6917</v>
+        <v>5.7321</v>
       </c>
       <c r="G17" t="n">
-        <v>4.9059</v>
+        <v>4.9261</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9493</v>
+        <v>2.9578</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9566</v>
+        <v>1.9683</v>
       </c>
       <c r="J17" t="n">
-        <v>2.5243</v>
+        <v>2.5132</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3378</v>
+        <v>2.327</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M17" t="n">
-        <v>2.3815</v>
+        <v>2.4129</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6115</v>
+        <v>0.6308</v>
       </c>
       <c r="O17" t="n">
-        <v>1.77</v>
+        <v>1.7821</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8605</v>
+        <v>-0.2726</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9043</v>
+        <v>-0.3139</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0438</v>
+        <v>0.0413</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.4829</v>
+        <v>4.2145</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6284</v>
+        <v>-0.1823</v>
       </c>
       <c r="F18" t="n">
-        <v>4.1113</v>
+        <v>4.3968</v>
       </c>
       <c r="G18" t="n">
-        <v>3.5575</v>
+        <v>3.5682</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4731</v>
+        <v>1.4843</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0844</v>
+        <v>2.084</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2429</v>
+        <v>1.2278</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9871</v>
+        <v>0.9825</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2558</v>
+        <v>0.2453</v>
       </c>
       <c r="M18" t="n">
-        <v>2.3147</v>
+        <v>2.3404</v>
       </c>
       <c r="N18" t="n">
-        <v>0.486</v>
+        <v>0.5018</v>
       </c>
       <c r="O18" t="n">
-        <v>1.8286</v>
+        <v>1.8386</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7796999999999999</v>
+        <v>-0.0578</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6956</v>
+        <v>-0.2232</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.08409999999999999</v>
+        <v>0.1655</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. AGADA</t>
+          <t>M. SANZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.1952</v>
+        <v>3.7627</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9746</v>
+        <v>0.7544</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2206</v>
+        <v>3.0084</v>
       </c>
       <c r="G19" t="n">
-        <v>2.4105</v>
+        <v>2.9718</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9337</v>
+        <v>1.2858</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4768</v>
+        <v>1.686</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3457</v>
+        <v>1.4631</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6367</v>
+        <v>0.1379</v>
       </c>
       <c r="L19" t="n">
-        <v>0.709</v>
+        <v>1.3252</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0647</v>
+        <v>1.5087</v>
       </c>
       <c r="N19" t="n">
-        <v>0.297</v>
+        <v>1.1479</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7678</v>
+        <v>0.3608</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0097</v>
+        <v>-0.8024</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6684</v>
+        <v>-0.4811</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6587</v>
+        <v>-0.3213</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SANZ</t>
+          <t>J. BATEMON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.9273</v>
+        <v>2.9315</v>
       </c>
       <c r="E20" t="n">
-        <v>0.415</v>
+        <v>-0.6926</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5124</v>
+        <v>3.6241</v>
       </c>
       <c r="G20" t="n">
-        <v>2.9621</v>
+        <v>4.1868</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2695</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6926</v>
+        <v>3.5169</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4765</v>
+        <v>1.5306</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1385</v>
+        <v>0.1681</v>
       </c>
       <c r="L20" t="n">
-        <v>1.338</v>
+        <v>1.3624</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4856</v>
+        <v>2.6562</v>
       </c>
       <c r="N20" t="n">
-        <v>1.131</v>
+        <v>0.5018</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3546</v>
+        <v>2.1545</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5878</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>-3.4145</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6226</v>
+        <v>0.1105</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8347</v>
+        <v>0.1019</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7879</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. BATEMON</t>
+          <t>C. AGADA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.875</v>
+        <v>2.6177</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0697</v>
+        <v>0.1143</v>
       </c>
       <c r="F21" t="n">
-        <v>2.8053</v>
+        <v>2.5034</v>
       </c>
       <c r="G21" t="n">
-        <v>4.2012</v>
+        <v>2.4135</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6827</v>
+        <v>0.928</v>
       </c>
       <c r="I21" t="n">
-        <v>3.5185</v>
+        <v>1.4855</v>
       </c>
       <c r="J21" t="n">
-        <v>1.572</v>
+        <v>1.3205</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1967</v>
+        <v>0.613</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3753</v>
+        <v>0.7075</v>
       </c>
       <c r="M21" t="n">
-        <v>2.6292</v>
+        <v>1.093</v>
       </c>
       <c r="N21" t="n">
-        <v>0.486</v>
+        <v>0.3149</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1432</v>
+        <v>0.778</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4025</v>
+        <v>-1.3658</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0348</v>
+        <v>-0.5666</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8075</v>
+        <v>-0.156</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7728</v>
+        <v>-0.4107</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>0.3155</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5236</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9243</v>
+        <v>-1.5967</v>
       </c>
       <c r="F22" t="n">
-        <v>2.4479</v>
+        <v>2.447</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3466</v>
+        <v>-1.3438</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6322</v>
+        <v>-0.621</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7144</v>
+        <v>-0.7228</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.025</v>
+        <v>-2.0472</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.111</v>
+        <v>-0.1174</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.914</v>
+        <v>-1.9298</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6784</v>
+        <v>0.7033</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5212</v>
+        <v>-0.5036</v>
       </c>
       <c r="O22" t="n">
-        <v>1.1995</v>
+        <v>1.2069</v>
       </c>
       <c r="P22" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0371</v>
+        <v>-0.7164</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7652</v>
+        <v>-0.4114</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2719</v>
+        <v>-0.305</v>
       </c>
       <c r="V22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7036</v>
+        <v>-0.5447</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7036</v>
+        <v>-0.5447</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2318</v>
+        <v>-0.2289</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2230,13 +2230,13 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2318</v>
+        <v>-0.2289</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4718</v>
+        <v>-0.3159</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4718</v>
+        <v>-0.3159</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7328</v>
+        <v>-1.9307</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6369</v>
+        <v>-5.0094</v>
       </c>
       <c r="F24" t="n">
-        <v>2.9041</v>
+        <v>3.0787</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.8965</v>
+        <v>-0.8935999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.7575</v>
+        <v>-1.7577</v>
       </c>
       <c r="I24" t="n">
-        <v>0.861</v>
+        <v>0.8641</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.2325</v>
+        <v>-2.2427</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.3071</v>
+        <v>-2.3172</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M24" t="n">
-        <v>1.336</v>
+        <v>1.3492</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5496</v>
+        <v>0.5595</v>
       </c>
       <c r="O24" t="n">
-        <v>0.7864</v>
+        <v>0.7896</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2979</v>
+        <v>0.101</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0907</v>
+        <v>-0.2627</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2072</v>
+        <v>0.3637</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.3758</v>
+        <v>-2.8573</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.5324</v>
+        <v>-4.1978</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1566</v>
+        <v>1.3406</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7882</v>
+        <v>0.8023</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4789</v>
+        <v>0.4878</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3092</v>
+        <v>0.3145</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0683</v>
+        <v>-0.0746</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.1803</v>
+        <v>-0.1864</v>
       </c>
       <c r="L25" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8565</v>
+        <v>0.877</v>
       </c>
       <c r="N25" t="n">
-        <v>0.6592</v>
+        <v>0.6741</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2567</v>
+        <v>-0.7491</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8347</v>
+        <v>-0.4811</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4219</v>
+        <v>-0.268</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>21.9317</v>
+        <v>23.5259</v>
       </c>
       <c r="E26" t="n">
-        <v>-11.3914</v>
+        <v>-11.6694</v>
       </c>
       <c r="F26" t="n">
-        <v>33.3232</v>
+        <v>35.1955</v>
       </c>
       <c r="G26" t="n">
-        <v>24.8428</v>
+        <v>24.8917</v>
       </c>
       <c r="H26" t="n">
-        <v>10.3021</v>
+        <v>10.3377</v>
       </c>
       <c r="I26" t="n">
-        <v>14.5406</v>
+        <v>14.5542</v>
       </c>
       <c r="J26" t="n">
-        <v>7.4142</v>
+        <v>7.225799999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>4.5761</v>
+        <v>4.458099999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>2.838200000000001</v>
+        <v>2.7675</v>
       </c>
       <c r="M26" t="n">
-        <v>17.4285</v>
+        <v>17.6661</v>
       </c>
       <c r="N26" t="n">
-        <v>5.726</v>
+        <v>5.8794</v>
       </c>
       <c r="O26" t="n">
-        <v>11.7024</v>
+        <v>11.7865</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q26" t="n">
-        <v>-21.549</v>
+        <v>-21.6249</v>
       </c>
       <c r="R26" t="n">
-        <v>19.281</v>
+        <v>19.3489</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.5991</v>
+        <v>-2.0424</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.4951</v>
+        <v>-2.4882</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.1041</v>
+        <v>0.4459000000000002</v>
       </c>
       <c r="V26" t="n">
-        <v>2.956600000000001</v>
+        <v>2.952799999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>5.2385</v>
+        <v>5.2182</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.282</v>
+        <v>-2.2654</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104596_W16.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104596_W16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.3562</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-5.2181</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104596_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-2.2654</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
